--- a/DE-trial-results/DE Trial — Scorecard (Responses).xlsx
+++ b/DE-trial-results/DE Trial — Scorecard (Responses).xlsx
@@ -957,6 +957,12 @@
       <c r="E9" s="8" t="s">
         <v>47</v>
       </c>
+      <c r="F9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>19</v>
+      </c>
       <c r="H9" s="8" t="s">
         <v>20</v>
       </c>

--- a/DE-trial-results/DE Trial — Scorecard (Responses).xlsx
+++ b/DE-trial-results/DE Trial — Scorecard (Responses).xlsx
@@ -5,13 +5,15 @@
   <sheets>
     <sheet state="visible" name="Form Responses 1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Form Responses 1'!$A$1:$O$14</definedName>
+  </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="51">
   <si>
     <t>Timestamp</t>
   </si>
@@ -58,9 +60,6 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>05 (jeremy)</t>
-  </si>
-  <si>
     <t>Non-SF</t>
   </si>
   <si>
@@ -79,9 +78,6 @@
     <t>5 (fix used exactly as given)</t>
   </si>
   <si>
-    <t>13 (nicholas)</t>
-  </si>
-  <si>
     <t>A4</t>
   </si>
   <si>
@@ -94,9 +90,6 @@
     <t>Cross environment does not work well (e.g command given were for bash, asked for a powershell command but the command did not work) but the solution was correct.</t>
   </si>
   <si>
-    <t>01 (yong jiun)</t>
-  </si>
-  <si>
     <t>SF</t>
   </si>
   <si>
@@ -109,9 +102,6 @@
     <t xml:space="preserve">slightly verbose. Could get straight to the point. </t>
   </si>
   <si>
-    <t>12 claudia</t>
-  </si>
-  <si>
     <t>a2</t>
   </si>
   <si>
@@ -121,10 +111,7 @@
     <t>talk too much. i just want the solution but it gives me grandmother story, i need to scroll and skimp through to find where the solution is and the istio problem idk what he talking so i had to prompt until it just gave me a fix that i can copy and paste bc im done reading non english</t>
   </si>
   <si>
-    <t>3 for willingness to use because  it will her her be more lazy and not learn</t>
-  </si>
-  <si>
-    <t>09 (jia qing)</t>
+    <t>3 for learning because  it will her her be more lazy and not learn</t>
   </si>
   <si>
     <t>A2</t>
@@ -134,70 +121,46 @@
   </si>
   <si>
     <t>there is no access to gitlab to troubleshoot potential issues in yaml file for configuration issues</t>
-  </si>
-  <si>
-    <t>07 (melvin)</t>
   </si>
   <si>
     <t>the prompt needs to provide more context to help the DE even if it can access the cluster, if not the AI will be stuck in a loop and will be unable to triage
 prompt used which made it take very long : "i have an issue with namespace i4-core ... my pod is stuck at crashloopbackoff"</t>
   </si>
   <si>
-    <t>02 (fAVIAN)</t>
-  </si>
-  <si>
     <t>a3</t>
   </si>
   <si>
     <t>K5</t>
   </si>
   <si>
-    <t>10 (jeng kit)</t>
-  </si>
-  <si>
     <t>i4</t>
   </si>
   <si>
     <t>It would be nice to have a comparable view, such as current config and change made config.</t>
   </si>
   <si>
-    <t>03 (zhiwen)</t>
-  </si>
-  <si>
     <t>k6</t>
   </si>
   <si>
     <t xml:space="preserve">i think the model response is short enough and concise withe actionable easy to fidn due to the bold "Fix -". </t>
   </si>
   <si>
-    <t>04 (anthony)</t>
-  </si>
-  <si>
     <t>K1</t>
   </si>
   <si>
     <t xml:space="preserve">Engineer may lose initial engineering instinct build up e.g. traditionally, engineers will need to brainstorm based on their past experience and skills. now with the use of AI, many a times i would imagine engineers will just skip this engineering troubleshooting steps and go straight to AI. quote ex hd STARLAB on this "with AI abstraction, the learning has to be even more deliberate to ensure that we truly understand the problem and the fixes". </t>
   </si>
   <si>
-    <t>11 (joash)</t>
-  </si>
-  <si>
     <t>i5</t>
   </si>
   <si>
     <t>Need to have a rough understanding of the issue first, but the AI does manage to pick up the issue along the way.</t>
   </si>
   <si>
-    <t>06 (clement)</t>
-  </si>
-  <si>
     <t>k7</t>
   </si>
   <si>
     <t>i3</t>
-  </si>
-  <si>
-    <t>08</t>
   </si>
   <si>
     <t>k5</t>
@@ -240,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -266,9 +229,6 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -351,6 +311,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:O14" displayName="Form_Responses" name="Form_Responses" id="1">
+  <autoFilter ref="$A$1:$O$14"/>
   <tableColumns count="15">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="DE number (name)" id="2"/>
@@ -635,35 +596,35 @@
       <c r="A2" s="3">
         <v>46258.61288642361</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="F2" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L2" s="4">
         <v>5.0</v>
@@ -678,32 +639,32 @@
       <c r="A3" s="3">
         <v>46258.65365421296</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="4">
+        <v>13.0</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K3" s="4">
         <v>4.0</v>
@@ -715,7 +676,7 @@
         <v>5.0</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="O3" s="6"/>
     </row>
@@ -723,44 +684,44 @@
       <c r="A4" s="3">
         <v>46258.68403783564</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="F4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="M4" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>31</v>
       </c>
       <c r="O4" s="6"/>
     </row>
@@ -768,35 +729,35 @@
       <c r="A5" s="7">
         <v>46259.49994037037</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>32</v>
+      <c r="B5" s="8">
+        <v>12.0</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I5" s="8">
         <v>3.0</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L5" s="8">
         <v>3.0</v>
@@ -805,42 +766,42 @@
         <v>5.0</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="7">
         <v>46259.62083017361</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>37</v>
+      <c r="B6" s="8">
+        <v>9.0</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I6" s="8">
         <v>3.0</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K6" s="8">
         <v>4.0</v>
@@ -852,7 +813,7 @@
         <v>5.0</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="O6" s="6"/>
     </row>
@@ -860,32 +821,32 @@
       <c r="A7" s="7">
         <v>46260.61985333334</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>41</v>
+      <c r="B7" s="8">
+        <v>7.0</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I7" s="8">
         <v>3.0</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K7" s="8">
         <v>4.0</v>
@@ -897,42 +858,42 @@
         <v>5.0</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="7">
         <v>46260.67324881944</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>43</v>
+      <c r="B8" s="8">
+        <v>2.0</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L8" s="8">
         <v>5.0</v>
@@ -945,35 +906,35 @@
       <c r="A9" s="7">
         <v>46260.74027400463</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>46</v>
+      <c r="B9" s="8">
+        <v>10.0</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L9" s="8">
         <v>5.0</v>
@@ -982,42 +943,42 @@
         <v>5.0</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="7">
         <v>46261.4590385301</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>49</v>
+      <c r="B10" s="8">
+        <v>3.0</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>25</v>
-      </c>
       <c r="G10" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L10" s="8">
         <v>5.0</v>
@@ -1026,42 +987,42 @@
         <v>5.0</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="7">
         <v>46261.556265266205</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>52</v>
+      <c r="B11" s="8">
+        <v>4.0</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L11" s="8">
         <v>5.0</v>
@@ -1070,42 +1031,42 @@
         <v>5.0</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="7">
         <v>46261.613253483796</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>55</v>
+      <c r="B12" s="8">
+        <v>11.0</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L12" s="8">
         <v>5.0</v>
@@ -1114,42 +1075,42 @@
         <v>5.0</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="7">
         <v>46262.43739306713</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>58</v>
+      <c r="B13" s="8">
+        <v>6.0</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L13" s="8">
         <v>5.0</v>
@@ -1162,35 +1123,35 @@
       <c r="A14" s="7">
         <v>46262.67354337963</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>61</v>
+      <c r="B14" s="8">
+        <v>8.0</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L14" s="8">
         <v>3.0</v>
@@ -1199,7 +1160,7 @@
         <v>5.0</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
